--- a/data/trans_orig/IP07A16-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>23880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,53%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>31152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>34863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37523</t>
+          <t>37642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53081</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32641</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48315</t>
+          <t>48464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70646</t>
+          <t>69751</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92015</t>
+          <t>91165</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43588</t>
+          <t>44633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39210</t>
+          <t>38927</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>54521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71932</t>
+          <t>71330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93186</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>28461</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55426</t>
+          <t>54890</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73184</t>
+          <t>73393</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33889</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52549</t>
+          <t>52501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>32491</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46337</t>
+          <t>46803</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>39330</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>125168</t>
+          <t>124831</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>151965</t>
+          <t>153826</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>141682</t>
+          <t>141420</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>170319</t>
+          <t>169806</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>273578</t>
+          <t>275238</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>314024</t>
+          <t>316352</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>105014</t>
+          <t>104195</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>131781</t>
+          <t>133081</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>122051</t>
+          <t>122537</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>150881</t>
+          <t>151439</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>235286</t>
+          <t>235392</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>274932</t>
+          <t>276879</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>42918</t>
+          <t>43151</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>54664</t>
+          <t>53926</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>78407</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24925</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>31480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>23767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>23184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37330</t>
+          <t>37378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45453</t>
+          <t>46127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35061</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>40567</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54915</t>
+          <t>55598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45755</t>
+          <t>45167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62215</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90632</t>
+          <t>91490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113647</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37903</t>
+          <t>37110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>38758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49864</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>71278</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44261</t>
+          <t>45192</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25044</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>38610</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>60248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79802</t>
+          <t>80650</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>39609</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51756</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>71393</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27950</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>28421</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>136720</t>
+          <t>136324</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>166065</t>
+          <t>166066</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>151263</t>
+          <t>153206</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>180084</t>
+          <t>181364</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>297427</t>
+          <t>297281</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>338077</t>
+          <t>336151</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>112265</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>140794</t>
+          <t>140634</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>97881</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>126731</t>
+          <t>125583</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>218388</t>
+          <t>219211</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>257341</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>35991</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>57795</t>
+          <t>57035</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27516</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>37730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51424</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>28682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48100</t>
+          <t>47835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>64357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15963</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>26862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30315</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43567</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78164</t>
+          <t>78397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55954</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72460</t>
+          <t>72943</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122041</t>
+          <t>121010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146014</t>
+          <t>146045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>27540</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>39262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79069</t>
+          <t>79309</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>50231</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39788</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65462</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85859</t>
+          <t>86577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35769</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>41505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>60518</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21934</t>
+          <t>21719</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>39961</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>36155</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>175604</t>
+          <t>176130</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>206501</t>
+          <t>206135</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>176698</t>
+          <t>175020</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>205980</t>
+          <t>205600</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>359875</t>
+          <t>359517</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>402798</t>
+          <t>403680</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>94742</t>
+          <t>95919</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>121978</t>
+          <t>123411</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>105947</t>
+          <t>106883</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>135120</t>
+          <t>135624</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>210389</t>
+          <t>208900</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>250466</t>
+          <t>251242</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>40895</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45288</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>69147</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15453</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
